--- a/results/log_pv_cap/log_pv_cap_baseline_tests.xlsx
+++ b/results/log_pv_cap/log_pv_cap_baseline_tests.xlsx
@@ -451,27 +451,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83.89***</t>
+          <t>80.78***</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>39.71***</t>
+          <t>43.00***</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8613.67***</t>
+          <t>8374.47***</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>77.41***</t>
+          <t>66.79***</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>831.59***</t>
+          <t>701.55***</t>
         </is>
       </c>
     </row>
@@ -483,27 +483,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.89***</t>
+          <t>80.78***</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11.18***</t>
+          <t>12.07***</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7161.77***</t>
+          <t>6671.62***</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.64***</t>
+          <t>17.17***</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>831.59***</t>
+          <t>701.55***</t>
         </is>
       </c>
     </row>
@@ -515,27 +515,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>83.89***</t>
+          <t>80.78***</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10.43***</t>
+          <t>10.83***</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7145.59***</t>
+          <t>6643.26***</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.12***</t>
+          <t>11.56***</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>831.59***</t>
+          <t>701.55***</t>
         </is>
       </c>
     </row>
